--- a/Request for Authority to Dispose of Record Form.xlsx
+++ b/Request for Authority to Dispose of Record Form.xlsx
@@ -1,22 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Employee Records Management System\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4F5165-F261-448C-9D43-3E6DBBB21DFB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="120" windowWidth="27795" windowHeight="12585"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>Lingayen, Pangasinan</t>
   </si>
@@ -39,17 +53,45 @@
     <t>Prepared by:</t>
   </si>
   <si>
-    <t>Period Covered</t>
-  </si>
-  <si>
     <t>Checked and reviewed by:</t>
+  </si>
+  <si>
+    <t>Entry</t>
+  </si>
+  <si>
+    <t>Retention Period</t>
+  </si>
+  <si>
+    <t>2026 (2 yrs)</t>
+  </si>
+  <si>
+    <t>PRDS 2009</t>
+  </si>
+  <si>
+    <t>2025 (2 yrs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub Category or Category </t>
+  </si>
+  <si>
+    <t>GRDS 
+2023</t>
+  </si>
+  <si>
+    <t>Entry without Sub Category or Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Entry</t>
+  </si>
+  <si>
+    <t>***Nothing Follows***</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +134,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -101,7 +151,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -223,74 +273,129 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -301,6 +406,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -349,7 +457,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -382,9 +490,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -417,6 +542,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -592,469 +734,289 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:P40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:K20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="11" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-    </row>
-    <row r="4" spans="2:11" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="2:11" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-    </row>
-    <row r="7" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="7" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="22" t="s">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="K7" s="22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="15"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-    </row>
-    <row r="9" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="1"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="1"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="1"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="1"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="K7" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="17"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+    </row>
+    <row r="9" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
+    </row>
+    <row r="10" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="23">
+        <v>99</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
+    </row>
+    <row r="11" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="25"/>
+      <c r="C11" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="23">
+        <v>2024</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="20"/>
+      <c r="C12" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="22">
+        <v>2023</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="24">
+        <v>88</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="22">
+        <v>2024</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="1"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
+      <c r="K14" s="21"/>
+    </row>
+    <row r="15" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="23">
+        <v>99</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="23"/>
+    </row>
+    <row r="16" spans="2:11" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25"/>
+      <c r="C16" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="23">
+        <v>2024</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="25"/>
+      <c r="C17" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="H18" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-    </row>
-    <row r="19" spans="2:16" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="N21" s="2"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="2"/>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B24" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-    </row>
-    <row r="25" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B26" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-    </row>
-    <row r="28" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="K28" s="22" t="s">
+      <c r="H19" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B29" s="15"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-    </row>
-    <row r="30" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="1"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="1"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-    </row>
-    <row r="32" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="1"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="1"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-    </row>
-    <row r="34" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="1"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="1"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="1"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-    </row>
-    <row r="37" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="1"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="H39" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-    </row>
-    <row r="40" spans="2:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="2:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="21">
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="H19:J19"/>
     <mergeCell ref="C7:I8"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
     <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C12:I12"/>
     <mergeCell ref="C13:I13"/>
     <mergeCell ref="C14:I14"/>
     <mergeCell ref="C15:I15"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="C31:I31"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="B24:K24"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="B26:K26"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:I29"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="K28:K29"/>
-    <mergeCell ref="C30:I30"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C32:I32"/>
-    <mergeCell ref="C33:I33"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="C37:I37"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1062,18 +1024,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
